--- a/processed_ruby_restored_xlsx/sc247_みるく９：撮影ごっこ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc247_みるく９：撮影ごっこ.ss.xlsx
@@ -499,8 +499,9 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>She usually cleans the common areas where everyone is,
-but in exchange she's careless about her own room.</t>
+          <t>She usually cleans the common areas where everyone
+is, but in exchange she's careless about her own
+room.</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -731,8 +732,8 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>「I found an old camera I bought a while back — mind if
-I take a few pictures？」</t>
+          <t>「I found an old camera I bought a while back — mind
+if I take a few pictures？」</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1004,8 +1005,8 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>I got carried away filming and commentating, and ended
-up being kicked out...</t>
+          <t>I got carried away filming and commentating, and
+ended up being kicked out...</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1143,8 +1144,8 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, I found it while I was cleaning. Mind if I film
-it for a bit？」</t>
+          <t>「Yeah, I found it while I was cleaning. Mind if I
+film it for a bit？」</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1265,8 +1266,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>I’d tried leaving it to Rurichiyo-chan this time since
-I got scolded for doing live commentary with
+          <t>I’d tried leaving it to Rurichiyo-chan this time
+since I got scolded for doing live commentary with
 Nono-chan, but it’s also a problem if she won’t do
 anything.</t>
         </is>
@@ -1373,8 +1374,8 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>…With Rurichiyo-chan, if I push it she might just tell
-me to get back to cleaning her room.</t>
+          <t>…With Rurichiyo-chan, if I push it she might just
+tell me to get back to cleaning her room.</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2499,8 +2500,8 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>…On the way to the cove the two of us, we stopped by a
-dagashi shop at Miru-chan's request.</t>
+          <t>…On the way to the cove the two of us, we stopped by
+a dagashi shop at Miru-chan's request.</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2608,8 +2609,8 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>She was grinning like crazy and had a big bag slung in
-her hand.</t>
+          <t>She was grinning like crazy and had a big bag slung
+in her hand.</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2945,7 +2946,8 @@
       <c r="B163" s="1" t="inlineStr">
         <is>
           <t>When we got to the cove, she changed into that
-swimsuit and we immediately started the photo session.</t>
+swimsuit and we immediately started the photo
+session.</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2960,8 +2962,8 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>Even if it was just pretend play, we might as well set
-the mood properly.</t>
+          <t>Even if it was just pretend play, we might as well
+set the mood properly.</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3128,8 +3130,8 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Having Miru-chan wear the HimePara swimsuit really got
-her all fired up.</t>
+          <t>Having Miru-chan wear the HimePara swimsuit really
+got her all fired up.</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3296,8 +3298,8 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>「Sounds great, sounds great… So, first let’s take some
-shots down by the water’s edge, okay？」</t>
+          <t>「Sounds great, sounds great… So, first let’s take
+some shots down by the water’s edge, okay？」</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3893,7 +3895,8 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>「That makes four now... so how many 'pieces' is that？」</t>
+          <t>「That makes four now... so how many 'pieces' is
+that？」</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3983,8 +3986,8 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>「...All right, then how about this time we try filming
-her while she's running？」</t>
+          <t>「...All right, then how about this time we try
+filming her while she's running？」</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4076,8 +4079,8 @@
       <c r="B237" s="1" t="inlineStr">
         <is>
           <t>I keep trying to film, focusing as best I can, but my
-hands shake and it drains my energy, so it's not going
-well.</t>
+hands shake and it drains my energy, so it's not
+going well.</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4289,8 +4292,8 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>「Hey, hey… Onii-chan, can't you be in the picture with
-me？」</t>
+          <t>「Hey, hey… Onii-chan, can't you be in the picture
+with me？」</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4532,9 +4535,9 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>We’d been playing a lot and our body temperatures were
-up, so I can’t help but get fluttery from that rising,
-sweet scent.</t>
+          <t>We’d been playing a lot and our body temperatures
+were up, so I can’t help but get fluttery from that
+rising, sweet scent.</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4625,8 +4628,8 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>Watching them fly side by side, they look like they’re
-getting along just like we are.</t>
+          <t>Watching them fly side by side, they look like
+they’re getting along just like we are.</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4734,8 +4737,8 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>…Even so, before the seagulls could fly away, a chance
-comes.</t>
+          <t>…Even so, before the seagulls could fly away, a
+chance comes.</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4840,8 +4843,8 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>I stop the recording and play the footage we just shot
-on the monitor.</t>
+          <t>I stop the recording and play the footage we just
+shot on the monitor.</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -5312,8 +5315,8 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>When I put on a serious air, Miru-chan straightened up
-too.</t>
+          <t>When I put on a serious air, Miru-chan straightened
+up too.</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5343,8 +5346,8 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>「I want to film more of Miru-chan's different faces...
-more of your cute moments...」</t>
+          <t>「I want to film more of Miru-chan's different
+faces... more of your cute moments...」</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5495,7 +5498,8 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t>「That's not it! Why are you sticking your penis out？!」</t>
+          <t>「That's not it! Why are you sticking your penis
+out？!」</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -6058,8 +6062,8 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>The kiss ended quickly, and before I knew it Miru-chan
-was looking at my face.</t>
+          <t>The kiss ended quickly, and before I knew it
+Miru-chan was looking at my face.</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -6105,8 +6109,8 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>But if I say, "We got it here~," it might all end just
-like that.</t>
+          <t>But if I say, "We got it here~," it might all end
+just like that.</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6226,8 +6230,8 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>「I guess there's no helping it... one more time, okay？
-Chu...」</t>
+          <t>「I guess there's no helping it... one more time,
+okay？ Chu...」</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -6288,8 +6292,8 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>I get more aroused than I expected, and my hands start
-to shake...</t>
+          <t>I get more aroused than I expected, and my hands
+start to shake...</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -6548,8 +6552,9 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t>She'd forgotten she'd decided it hadn't been recorded,
-and she hurriedly tries to cover it up again.</t>
+          <t>She'd forgotten she'd decided it hadn't been
+recorded, and she hurriedly tries to cover it up
+again.</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -6792,8 +6797,8 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>「Fuhihi！ Naughty Onii-chan, smooch... smooch！ Wanna do
-even more, okay？ Smoooch！」</t>
+          <t>「Fuhihi！ Naughty Onii-chan, smooch... smooch！ Wanna
+do even more, okay？ Smoooch！」</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -6838,8 +6843,8 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>When Miru-chan saw that I was feeling it, she couldn't
-help but start enjoying teasing me.</t>
+          <t>When Miru-chan saw that I was feeling it, she
+couldn't help but start enjoying teasing me.</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -6869,8 +6874,8 @@
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t>「Ehehe... ngggh, smooch... smooch-ah！  Smooch... nngh！
-Make sure... you take it, okay？」</t>
+          <t>「Ehehe... ngggh, smooch... smooch-ah！  Smooch...
+nngh！  Make sure... you take it, okay？」</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -7132,8 +7137,8 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t>But the sensitized penis immediately trembled, craving
-the next wave of feeling.</t>
+          <t>But the sensitized penis immediately trembled,
+craving the next wave of feeling.</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -7604,8 +7609,8 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>Before I can continue speaking, the tip of my penis is
-pulled into her mouth.</t>
+          <t>Before I can continue speaking, the tip of my penis
+is pulled into her mouth.</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -8232,8 +8237,8 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>And right now my head didn't have the capacity to even
-think about that much...</t>
+          <t>And right now my head didn't have the capacity to
+even think about that much...</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8263,8 +8268,8 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>「See, when you put it into the hole, you’ve got to wet
-it plenty, Onii-chan says…」</t>
+          <t>「See, when you put it into the hole, you’ve got to
+wet it plenty, Onii-chan says…」</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8460,7 +8465,8 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>Still, I wondered what was going to happen to me next.</t>
+          <t>Still, I wondered what was going to happen to me
+next.</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8551,7 +8557,8 @@
       </c>
       <c r="B530" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan's tongue reached out to my urethral opening.</t>
+          <t>Miru-chan's tongue reached out to my urethral
+opening.</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -8764,8 +8771,8 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>The instant warm, drippy saliva was pressed against my
-urethral opening, my head nearly exploded.</t>
+          <t>The instant warm, drippy saliva was pressed against
+my urethral opening, my head nearly exploded.</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -9777,9 +9784,9 @@
       </c>
       <c r="B610" s="1" t="inlineStr">
         <is>
-          <t>Although the stimulation was milder than when only the
-tip was being teased, being fully taken into her mouth
-felt so good…！</t>
+          <t>Although the stimulation was milder than when only
+the tip was being teased, being fully taken into her
+mouth felt so good…！</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -9948,7 +9955,8 @@
       </c>
       <c r="B621" s="1" t="inlineStr">
         <is>
-          <t>「Fuhi！　Fuhihi！　Rahihyae！　Chuu！　Chubu！　Chububu！　Djupu！」</t>
+          <t>「Fuhi！　Fuhihi！　Rahihyae！　Chuu！　Chubu！　Chububu！　Djupu！
+」</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -9993,8 +10001,8 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan seized the moment and launched into a sprint
-of suction.</t>
+          <t>Miru-chan seized the moment and launched into a
+sprint of suction.</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -10010,8 +10018,8 @@
       <c r="B625" s="1" t="inlineStr">
         <is>
           <t>My conscious mind wanted to keep filming this image,
-wanted to keep shooting, but my instincts were telling
-me the exact opposite.</t>
+wanted to keep shooting, but my instincts were
+telling me the exact opposite.</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10271,8 +10279,8 @@
       </c>
       <c r="B642" s="1" t="inlineStr">
         <is>
-          <t>An amount that even she is surprised by spills out and
-fills Miru-chan's mouth...！</t>
+          <t>An amount that even she is surprised by spills out
+and fills Miru-chan's mouth...！</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -10394,8 +10402,8 @@
       </c>
       <c r="B650" s="1" t="inlineStr">
         <is>
-          <t>My head, overwhelmed by pleasure, screamed, Here！ Take
-a picture of here！</t>
+          <t>My head, overwhelmed by pleasure, screamed, Here！
+Take a picture of here！</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -10533,8 +10541,8 @@
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>「Haah... ah！ Amazing... it's amazing, Miru-chan... you
-got such a horny, cute shot！」</t>
+          <t>「Haah... ah！ Amazing... it's amazing, Miru-chan...
+you got such a horny, cute shot！」</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -10658,8 +10666,8 @@
       </c>
       <c r="B667" s="1" t="inlineStr">
         <is>
-          <t>The intense feeling of ejaculation makes even catching
-my breath a real task.</t>
+          <t>The intense feeling of ejaculation makes even
+catching my breath a real task.</t>
         </is>
       </c>
       <c r="C667" t="n">
@@ -10675,7 +10683,8 @@
       <c r="B668" s="1" t="inlineStr">
         <is>
           <t>But my affection swells so much that, even though I
-have no words left, I end up calling out to Miru-chan.</t>
+have no words left, I end up calling out to
+Miru-chan.</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -11043,8 +11052,9 @@
       </c>
       <c r="B692" s="1" t="inlineStr">
         <is>
-          <t>When I said it hesitantly, Miru-chan opened her mouth,
-glancing back and forth between my penis and my face.</t>
+          <t>When I said it hesitantly, Miru-chan opened her
+mouth, glancing back and forth between my penis and
+my face.</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -11224,8 +11234,8 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>The sweet back-and-forth made me feel ticklish, but my
-anticipation and arousal won out.</t>
+          <t>The sweet back-and-forth made me feel ticklish, but
+my anticipation and arousal won out.</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -11363,8 +11373,8 @@
       </c>
       <c r="B713" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan winces at the sting of the penis going in… I
-make sure to capture that expression on camera too.</t>
+          <t>Miru-chan winces at the sting of the penis going in…
+I make sure to capture that expression on camera too.</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -11592,8 +11602,9 @@
       <c r="B728" s="1" t="inlineStr">
         <is>
           <t>…Miru-chan was probably aware she was being
-photographed when she said it, but what she’s thinking
-is cute because it’s different from what I’m thinking.</t>
+photographed when she said it, but what she’s
+thinking is cute because it’s different from what I’m
+thinking.</t>
         </is>
       </c>
       <c r="C728" t="n">
@@ -11929,8 +11940,8 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. I want you to explain what you're feeling… with
-your mouth, Miru-chan.」</t>
+          <t>「Yeah. I want you to explain what you're feeling…
+with your mouth, Miru-chan.」</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -11975,8 +11986,8 @@
       </c>
       <c r="B753" s="1" t="inlineStr">
         <is>
-          <t>She said she'd give it a try, but Miru-chan is lost in
-thought.</t>
+          <t>She said she'd give it a try, but Miru-chan is lost
+in thought.</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -12312,8 +12323,8 @@
       </c>
       <c r="B775" s="1" t="inlineStr">
         <is>
-          <t>Just listening to Miru-chan's words sends shivers down
-my spine.</t>
+          <t>Just listening to Miru-chan's words sends shivers
+down my spine.</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -12527,8 +12538,8 @@
       </c>
       <c r="B789" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, though she stammers, still tries to explain
-properly.</t>
+          <t>Miru-chan, though she stammers, still tries to
+explain properly.</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12790,8 +12801,8 @@
       </c>
       <c r="B806" s="1" t="inlineStr">
         <is>
-          <t>We're in the middle of sex, so she really doesn't have
-the leeway to think.</t>
+          <t>We're in the middle of sex, so she really doesn't
+have the leeway to think.</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -12867,8 +12878,8 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>As I pushed my hips in while saying it, Miru-chan told
-me exactly what to do.</t>
+          <t>As I pushed my hips in while saying it, Miru-chan
+told me exactly what to do.</t>
         </is>
       </c>
       <c r="C811" t="n">
@@ -13177,8 +13188,8 @@
       </c>
       <c r="B831" s="1" t="inlineStr">
         <is>
-          <t>Despite her words, Miru-chan's body was already primed
-for sex.</t>
+          <t>Despite her words, Miru-chan's body was already
+primed for sex.</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -13193,7 +13204,8 @@
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
-          <t>Her voice rang out higher and higher, intoxicating me.</t>
+          <t>Her voice rang out higher and higher, intoxicating
+me.</t>
         </is>
       </c>
       <c r="C832" t="n">
@@ -13223,7 +13235,8 @@
       </c>
       <c r="B834" s="1" t="inlineStr">
         <is>
-          <t>「Next... I want you to tell me about your body, okay？」</t>
+          <t>「Next... I want you to tell me about your body,
+okay？」</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -13576,8 +13589,8 @@
       </c>
       <c r="B857" s="1" t="inlineStr">
         <is>
-          <t>It's kind of like I'm being led, but Miru-chan's words
-are starting to sound like they're inviting me.</t>
+          <t>It's kind of like I'm being led, but Miru-chan's
+words are starting to sound like they're inviting me.</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -13974,8 +13987,8 @@
       </c>
       <c r="B883" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan stood there with her mouth agape, exposing a
-shameless expression.</t>
+          <t>Miru-chan stood there with her mouth agape, exposing
+a shameless expression.</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -14113,8 +14126,8 @@
       </c>
       <c r="B892" s="1" t="inlineStr">
         <is>
-          <t>And when the sound gets louder, it starts to feel like
-she's telling me her pussy is feeling it.</t>
+          <t>And when the sound gets louder, it starts to feel
+like she's telling me her pussy is feeling it.</t>
         </is>
       </c>
       <c r="C892" t="n">
@@ -14265,7 +14278,8 @@
       </c>
       <c r="B902" s="1" t="inlineStr">
         <is>
-          <t>「U… unno…？ It's all melty and squelchy… I can't tell…」</t>
+          <t>「U… unno…？ It's all melty and squelchy… I can't
+tell…」</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -14297,7 +14311,8 @@
       <c r="B904" s="1" t="inlineStr">
         <is>
           <t>Her vagina was already like a reservoir of love
-juices, completely turned into a filthy, horny pussy…！</t>
+juices, completely turned into a filthy, horny
+pussy…！</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -14508,8 +14523,8 @@
       </c>
       <c r="B918" s="1" t="inlineStr">
         <is>
-          <t>I'm feeling pretty horny too, but basically it's still
-an extension of our playing at being a shoot, I
+          <t>I'm feeling pretty horny too, but basically it's
+still an extension of our playing at being a shoot, I
 guess...</t>
         </is>
       </c>
@@ -14676,7 +14691,8 @@
       <c r="B929" s="1" t="inlineStr">
         <is>
           <t>Her fired-up boldness made Miru-chan shout out, but
-the way she gets embarrassed right after is great too.</t>
+the way she gets embarrassed right after is great
+too.</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -14845,8 +14861,8 @@
       </c>
       <c r="B940" s="1" t="inlineStr">
         <is>
-          <t>Words that come out naturally resonate especially high
-and loud.</t>
+          <t>Words that come out naturally resonate especially
+high and loud.</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -15351,9 +15367,9 @@
       </c>
       <c r="B973" s="1" t="inlineStr">
         <is>
-          <t>Even at this point Miru-chan is honest enough to think
-about commentating, but it seems she's finally lost
-her composure.</t>
+          <t>Even at this point Miru-chan is honest enough to
+think about commentating, but it seems she's finally
+lost her composure.</t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -16507,8 +16523,8 @@
       </c>
       <c r="B1048" s="1" t="inlineStr">
         <is>
-          <t>Then, the semen that had been building up from holding
-back earlier spurts out loudly...！</t>
+          <t>Then, the semen that had been building up from
+holding back earlier spurts out loudly...！</t>
         </is>
       </c>
       <c r="C1048" t="n">
@@ -16538,7 +16554,8 @@
       </c>
       <c r="B1050" s="1" t="inlineStr">
         <is>
-          <t>「Ha haa, ha！ Aahh… ah, nngh, ha！ So full… aren’t you…」</t>
+          <t>「Ha haa, ha！ Aahh… ah, nngh, ha！ So full… aren’t
+you…」</t>
         </is>
       </c>
       <c r="C1050" t="n">
@@ -16736,8 +16753,8 @@
       </c>
       <c r="B1063" s="1" t="inlineStr">
         <is>
-          <t>I'm really happy, but Miru-chan turns her face red and
-looks down.</t>
+          <t>I'm really happy, but Miru-chan turns her face red
+and looks down.</t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -16933,8 +16950,8 @@
       </c>
       <c r="B1076" s="1" t="inlineStr">
         <is>
-          <t>「Could you do a closing line for me...？ To the camera,
-ready, say！」</t>
+          <t>「Could you do a closing line for me...？ To the
+camera, ready, say！」</t>
         </is>
       </c>
       <c r="C1076" t="n">

--- a/processed_ruby_restored_xlsx/sc247_みるく９：撮影ごっこ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc247_みるく９：撮影ごっこ.ss.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>「W-wait... Janitor-sensei...？」</t>
+          <t>W-wait... Janitor-sensei...？</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -3177,8 +3177,8 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>I don’t know what about her is princess-y, but she’s
-so ridiculously cute, so who cares！</t>
+          <t>I don’t know what about them is princess-y, but
+they’re so ridiculously cute, so who cares！</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3359,8 +3359,8 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>「Alright, next I want you to sit down. I also want a
-shot of the wave rolling in.」</t>
+          <t>Alright, next I want you to sit down. I also want a
+shot of the wave rolling in.</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>What I had pictured was her running while splashing
+          <t>What I had pictured was them running while splashing
 and giggling in the waves...</t>
         </is>
       </c>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>Did she want to be in the picture with me？</t>
+          <t>Did they want to be in the picture with me？</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>Miruku</t>
+          <t>Miru-chan</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6874,8 +6874,8 @@
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t>「Ehehe... ngggh, smooch... smooch-ah！  Smooch...
-nngh！  Make sure... you take it, okay？」</t>
+          <t>Ehehe... ngggh, smooch... smooch-ah！  Smooch... nngh！
+Make sure... you take it, okay？</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>「Miru-chan... not there！ If you do it that much...」</t>
+          <t>Miru-chan... not there！ If you do it that much...</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7839,8 +7839,8 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>「smooch, smooch！ smooch-slap...slurp！ lick,
-lerrk...lick！ nngh, chup！」</t>
+          <t>smooch, smooch！ smooch-slap...slurp！ lick,
+lerrk...lick！ nngh, chup！</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7994,7 +7994,7 @@
       <c r="B493" s="1" t="inlineStr">
         <is>
           <t>Her face with my penis in her mouth… did I get a good
-shot of it…！？</t>
+shot of it…！？"</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -8908,8 +8908,8 @@
       </c>
       <c r="B553" s="1" t="inlineStr">
         <is>
-          <t>Even I can't understand what just happened a moment
-ago, and no amount of thinking will catch up.</t>
+          <t>She herself can't understand what that was a moment
+ago, and thinking about it won't catch up to it.</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -9078,7 +9078,7 @@
       <c r="B564" s="1" t="inlineStr">
         <is>
           <t>It's a different sensation than ejaculation, like
-having my seed taken away...</t>
+having his seed taken away...</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>...The feeling of my semen being taken away implants
+          <t>...The feeling of his semen being taken away implants
 the image of it being squeezed out.</t>
         </is>
       </c>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="B591" s="1" t="inlineStr">
         <is>
-          <t>「Mi-Miru-chan！ Make a peace sign！」</t>
+          <t>Mi-Miru-chan！ Make a peace sign！</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -10386,8 +10386,8 @@
       </c>
       <c r="B649" s="1" t="inlineStr">
         <is>
-          <t>Even while continuing to cum, I desperately reach for
-a peace sign.</t>
+          <t>Even while continuing to cum, they desperately reach
+for a peace sign.</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="B651" s="1" t="inlineStr">
         <is>
-          <t>Because she sent such a mysterious order.</t>
+          <t>Because they sent such a mysterious order.</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -10541,8 +10541,8 @@
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>「Haah... ah！ Amazing... it's amazing, Miru-chan...
-you got such a horny, cute shot！」</t>
+          <t>Haah... ah！ Amazing... it's amazing, Miru-chan... you
+got such a horny, cute shot！</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -10621,7 +10621,7 @@
       <c r="B664" s="1" t="inlineStr">
         <is>
           <t>But to my eyes, it even looks like a face doused in
-semen, like she’s all hot and horny….</t>
+semen, like they’re all hot and horny….</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="B672" s="1" t="inlineStr">
         <is>
-          <t>「I-I'm okay... but wow, that was amazing...！」</t>
+          <t>I-I'm okay... but wow, that was amazing...！</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="B719" s="1" t="inlineStr">
         <is>
-          <t>「M-Moooooo—！」</t>
+          <t>M-Moooooo—！</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>「Uu... okay, I'll try it... nnngh...」</t>
+          <t>Uu... okay, I」ll try it... nnngh...</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>「O-Onii-chan's... my... penis is...」</t>
+          <t>「O-Onii-chan's... his... penis is...」</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -13525,8 +13525,8 @@
       </c>
       <c r="B853" s="1" t="inlineStr">
         <is>
-          <t>「Mm... Well then, I'll stir it up for you moooore...
-Here！」</t>
+          <t>Mm... Well then, I'll stir it up for you moooore...
+Here！</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -13573,8 +13573,8 @@
       </c>
       <c r="B856" s="1" t="inlineStr">
         <is>
-          <t>「Fuaaah... Ah！ Aahhh...！ Ah, no... I'm being worked
-over...！」</t>
+          <t>Fuaaah... Ah！ Aahhh...！ Ah, no... I」m being worked
+over...！</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="B869" s="1" t="inlineStr">
         <is>
-          <t>「Nn？ Ah, ahh... um, uh—！」</t>
+          <t>Nn？ Ah, ahh... um, uh—！</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -13789,8 +13789,8 @@
       </c>
       <c r="B870" s="1" t="inlineStr">
         <is>
-          <t>Furthermore, I lifted Miru-chan's hips as I thrust my
-penis in.</t>
+          <t>Furthermore, he lifted Miru-chan's hips as he thrust
+his penis in.</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="B910" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh！ I was just about to say that...」</t>
+          <t>Nnnh！ I was just about to say that...</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -15088,8 +15088,8 @@
       </c>
       <c r="B955" s="1" t="inlineStr">
         <is>
-          <t>「Ugh！ Ahh！ Ah, ah！ Haaaahh！ Y-... it's amazing, it's
-amazing... nn！ Nn！」</t>
+          <t>Ugh！ Ahh！ Ah, ah！ Haaaahh！ Y-... it's amazing, it's
+amazing... nn！ Nn！</t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -15120,9 +15120,9 @@
       </c>
       <c r="B957" s="1" t="inlineStr">
         <is>
-          <t>I brace my hips hard and, rubbing against the soft
-flesh of the vaginal walls, try for an even deeper
-penetration…！</t>
+          <t>They brace their hips hard and, rubbing against the
+soft flesh of the vaginal walls, try for an even
+deeper penetration…！</t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -15152,8 +15152,8 @@
       </c>
       <c r="B959" s="1" t="inlineStr">
         <is>
-          <t>「Uwaaah...! What is this?! My stomach—it's all
-squished...!」</t>
+          <t>Uwaaah...! What is this?! My stomach—it's all
+squished...!</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>「Aahh, nnngh！ Miru-chan, does it feel good？」</t>
+          <t>Aahh, nnngh！ Miru-chan, does it feel good？</t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -15213,8 +15213,8 @@
       </c>
       <c r="B963" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah... yeah, it feels so good！ This is amazing！
-Ah... yes, uaaah！」</t>
+          <t>Ah, ah... yeah, it feels so good！ This is amazing！
+Ah... yes, uaaah！</t>
         </is>
       </c>
       <c r="C963" t="n">
@@ -15351,8 +15351,8 @@
       </c>
       <c r="B972" s="1" t="inlineStr">
         <is>
-          <t>「Mmm...nn！ I can't cum properly... nna！ I can't hold
-on... not anymore！」</t>
+          <t>Mmm...nn！ I can't cum properly... nna！ I can't hold
+on... not anymore！</t>
         </is>
       </c>
       <c r="C972" t="n">
@@ -15946,8 +15946,8 @@
       </c>
       <c r="B1011" s="1" t="inlineStr">
         <is>
-          <t>「Aah, nuu！ You idiot, you idiot！ Onii-chan, you
-pervert！」</t>
+          <t>Aah, nuu！ You idiot, you idiot！ Onii-chan, you
+pervert！</t>
         </is>
       </c>
       <c r="C1011" t="n">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B1023" s="1" t="inlineStr">
         <is>
-          <t>When I say "I love you," she says it back — her
+          <t>When I say "I love you," they say it back — their
 cuteness makes my head feel like it's going to
 explode.</t>
         </is>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="B1036" s="1" t="inlineStr">
         <is>
-          <t>「Wahhh! It's amazing... ah— it's coming!」</t>
+          <t>Wahhh! It's amazing... ah— it's coming!</t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -16399,8 +16399,7 @@
       </c>
       <c r="B1040" s="1" t="inlineStr">
         <is>
-          <t>「Uwaaah！ That feels...so good！ Nnnh...nnn！
-Fuuuhhh...！」</t>
+          <t>Uwaaah！ That feels...so good！ Nnnh...nnn！ Fuuuhhh...！</t>
         </is>
       </c>
       <c r="C1040" t="n">
@@ -16491,8 +16490,8 @@
       </c>
       <c r="B1046" s="1" t="inlineStr">
         <is>
-          <t>「Hah, haa...！ It's still... coming...！ So much... so
-much... mmm！」</t>
+          <t>Hah, haa...！ It's still... coming...！ So much... so
+much... mmm！</t>
         </is>
       </c>
       <c r="C1046" t="n">
@@ -16507,7 +16506,7 @@
       </c>
       <c r="B1047" s="1" t="inlineStr">
         <is>
-          <t>While ejaculations were continuing, I pulled out my
+          <t>While ejaculations were continuing, he pulled out his
 penis and immediately passed out.</t>
         </is>
       </c>
